--- a/lecture_tutorials/1B_lec_tut_lin_reg_example.xlsx
+++ b/lecture_tutorials/1B_lec_tut_lin_reg_example.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hendrik Mattern\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hmattern\Documents\git_project\physics\lecture_tutorials\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7958DE9D-919D-4FB1-97D7-E101AA3C271D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4477E10E-CA3E-46C7-BC4F-511A23CE9E1C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -173,16 +173,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>4</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6.25</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>15.209999999999999</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>16</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0</c:v>
@@ -254,16 +254,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>4</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6.25</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>15.209999999999999</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>16</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0</c:v>
@@ -293,34 +293,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>0.30752307326376954</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.41974979520509215</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.86666154124698125</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.90606559028415679</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.10800890092364046</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.10800890092364046</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.10800890092364046</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.10800890092364046</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.10800890092364046</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.10800890092364046</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -783,9 +783,9 @@
       <c r="E4" t="s">
         <v>7</v>
       </c>
-      <c r="F4">
+      <c r="F4" t="e">
         <f>SLOPE(A5:A14, C5:C14)</f>
-        <v>4.987854308503227E-2</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -793,22 +793,22 @@
         <v>0.25</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C5">
         <f t="shared" ref="C5:C14" si="0">B5^2</f>
-        <v>4</v>
-      </c>
-      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="D5" t="e">
         <f t="shared" ref="D5:D14" si="1">$F$4*C5 + $F$6</f>
-        <v>0.30752307326376954</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
-      <c r="F5">
+      <c r="F5" t="e">
         <f>2*F4</f>
-        <v>9.9757086170064541E-2</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -816,22 +816,22 @@
         <v>0.5</v>
       </c>
       <c r="B6">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="C6">
         <f t="shared" si="0"/>
-        <v>6.25</v>
-      </c>
-      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="D6" t="e">
         <f t="shared" si="1"/>
-        <v>0.41974979520509215</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
       </c>
-      <c r="F6">
+      <c r="F6" t="e">
         <f>INTERCEPT(A5:A14, C5:C14)</f>
-        <v>0.10800890092364046</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -839,22 +839,22 @@
         <v>0.75</v>
       </c>
       <c r="B7">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
-        <v>15.209999999999999</v>
-      </c>
-      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="D7" t="e">
         <f t="shared" si="1"/>
-        <v>0.86666154124698125</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
-      <c r="F7">
+      <c r="F7" t="e">
         <f>RSQ(A5:A14, C5:C14)</f>
-        <v>0.89701571884122044</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -862,15 +862,15 @@
         <v>1</v>
       </c>
       <c r="B8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C8">
         <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="D8" t="e">
         <f t="shared" si="1"/>
-        <v>0.90606559028415679</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -878,9 +878,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D9">
+      <c r="D9" t="e">
         <f t="shared" si="1"/>
-        <v>0.10800890092364046</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -888,9 +888,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D10">
+      <c r="D10" t="e">
         <f t="shared" si="1"/>
-        <v>0.10800890092364046</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -898,9 +898,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D11">
+      <c r="D11" t="e">
         <f t="shared" si="1"/>
-        <v>0.10800890092364046</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -908,9 +908,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D12">
+      <c r="D12" t="e">
         <f t="shared" si="1"/>
-        <v>0.10800890092364046</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -918,9 +918,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D13">
+      <c r="D13" t="e">
         <f t="shared" si="1"/>
-        <v>0.10800890092364046</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -928,9 +928,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D14">
+      <c r="D14" t="e">
         <f t="shared" si="1"/>
-        <v>0.10800890092364046</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
   </sheetData>
